--- a/data/trans_orig/Q5410A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5410A_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>457</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>437</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>696</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>995</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>386</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>403</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>380</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>510</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>314</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>14085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10338</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14313</t>
+          <t>15894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>13278</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>19080</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>406</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>438</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15911</t>
+          <t>19734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>14749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,17 +1929,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>42470</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>42470</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>42470</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>46295</t>
+          <t>51269</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>46295</t>
+          <t>51269</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>46295</t>
+          <t>51269</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>20662</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24673</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>409</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>412</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
